--- a/output/pdf_financials_xlsx/HG.xlsx
+++ b/output/pdf_financials_xlsx/HG.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/HG.xlsx
+++ b/output/pdf_financials_xlsx/HG.xlsx
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.026478</v>
+        <v>0.026478</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-0.057863</v>
+        <v>0.057863</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.048727</v>
+        <v>0.048727</v>
       </c>
     </row>
     <row r="6">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.765656</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.726035</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.69073</v>
       </c>
     </row>
     <row r="10">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.382936</v>
+        <v>1.148592</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.296005</v>
+        <v>1.02204</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.417289</v>
+        <v>1.108019</v>
       </c>
     </row>
     <row r="11">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2621,7 +2621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>-0.026478</v>
+        <v>0.026478</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-0.057863</v>
+        <v>0.057863</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.048727</v>
+        <v>0.048727</v>
       </c>
     </row>
     <row r="75">
@@ -5264,7 +5264,11 @@
           <t>Travel and promotion</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>0.765656</v>
       </c>
@@ -5622,7 +5626,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5631,8 +5635,10 @@
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>4.869723</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" s="5" t="n">
         <v>4.869723</v>
@@ -5649,7 +5655,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5680,7 +5686,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5711,7 +5717,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5742,7 +5748,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5773,7 +5779,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5786,8 +5792,10 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E104" s="5" t="n">
-        <v>-5.298016</v>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F104" s="5" t="n">
         <v>-5.298016</v>
@@ -5804,7 +5812,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5813,8 +5821,10 @@
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" s="5" t="n">
-        <v>4.672635</v>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F105" s="5" t="n">
         <v>4.672635</v>
@@ -5831,7 +5841,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5862,7 +5872,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5893,7 +5903,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5924,7 +5934,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5955,7 +5965,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5986,7 +5996,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6015,7 +6025,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note                #</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6259,7 +6269,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6288,7 +6298,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6319,7 +6329,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6350,7 +6360,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6381,7 +6391,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6414,22 +6424,20 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Private placement 9 54,542,400 3,943,640 1,048,167 -</t>
+          <t>Balance, September 30, 2023 174,775,224 11,600,057 3,394,318 (276,884)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" s="5" t="n">
-        <v>4.991807</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.869723</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>-9.847768</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6445,17 +6453,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Share issue costs 9 - (462,854) 118,685 -</t>
+          <t>Private placement 9 54,542,400 3,943,640 1,048,167 -</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" s="5" t="n">
-        <v>-0.344169</v>
+        <v>4.991807</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -6476,17 +6484,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Shares issued for warrant exercise 9 1,492,750 95,502 (39,000) -</t>
+          <t>Share issue costs 9 - (462,854) 118,685 -</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" s="5" t="n">
-        <v>0.056502</v>
+        <v>-0.344169</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -6507,24 +6515,117 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Note #</t>
+          <t>Note              #</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Stock-based compensation 9 - - 396,788 -</t>
+          <t>Shares issued for warrant exercise 9 1,492,750 95,502 (39,000) -</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" s="5" t="n">
+        <v>0.056502</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Note              #</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Stock-based compensation 9 - - 396,788 -</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" s="5" t="n">
         <v>0.396788</v>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Note              #</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - - 33,970</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>-5.298016</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>-5.331986</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Note              #</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Balance, September 30, 2024 230,810,374 15,176,345 4,918,958 (242,914)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="5" t="n">
+        <v>4.672635</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>-15.179754</v>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/HG.xlsx
+++ b/output/pdf_financials_xlsx/HG.xlsx
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.394318</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.918958</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.799594</v>
       </c>
     </row>
     <row r="93">
@@ -3233,7 +3233,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3615,7 +3619,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>3.394318</v>
       </c>

--- a/output/pdf_financials_xlsx/HG.xlsx
+++ b/output/pdf_financials_xlsx/HG.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.148592</v>
+        <v>4.824225</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.02204</v>
+        <v>5.175721</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.108019</v>
+        <v>6.032584</v>
       </c>
     </row>
     <row r="11">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.452469</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.780966</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>8.737793</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.452469</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.780966</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>8.737793</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.565728</v>
+        <v>0.113259</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.90763</v>
+        <v>0.126664</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>9.003126999999999</v>
+        <v>0.265334</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">

--- a/output/pdf_financials_xlsx/HG.xlsx
+++ b/output/pdf_financials_xlsx/HG.xlsx
@@ -4200,7 +4200,11 @@
           <t>Shares issued for cash, net 8</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -4649,7 +4653,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>1.913231</v>
       </c>
